--- a/ig/DM-JUIN-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="2393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="2397">
   <si>
     <t>Property</t>
   </si>
@@ -3691,6 +3691,18 @@
   </si>
   <si>
     <t>Drainage bronchique</t>
+  </si>
+  <si>
+    <t>0897</t>
+  </si>
+  <si>
+    <t>Drainage Vaccination épidémie Grippe</t>
+  </si>
+  <si>
+    <t>0898</t>
+  </si>
+  <si>
+    <t>Dépistage du diabète</t>
   </si>
   <si>
     <t>0909</t>
@@ -7453,7 +7465,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1184"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16921,15 +16933,31 @@
         <v>2390</v>
       </c>
       <c r="B1183" t="s" s="2">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="1184">
       <c r="A1184" t="s" s="2">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="B1184" t="s" s="2">
-        <v>2392</v>
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="s" s="2">
+        <v>2394</v>
+      </c>
+      <c r="B1185" t="s" s="2">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="s" s="2">
+        <v>2395</v>
+      </c>
+      <c r="B1186" t="s" s="2">
+        <v>2396</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-JUIN-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20250625120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-06-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
